--- a/output/laminas_provinciales/prov_i_ingr_mean_a_2022_metropolitana.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_mean_a_2022_metropolitana.xlsx
@@ -80,7 +80,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:08</t>
+    <t xml:space="preserve">2026-09-09 22:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_ingr_mean_a_2022_metropolitana.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_mean_a_2022_metropolitana.xlsx
@@ -80,7 +80,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:05</t>
+    <t xml:space="preserve">2026-09-17 13:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -991,10 +991,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>573331.38</v>
+        <v>501433.28</v>
       </c>
     </row>
     <row r="3">
@@ -1007,26 +1007,26 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>380662.78</v>
+        <v>573331.38</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>297186.25</v>
+        <v>380662.78</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>501433.28</v>
+        <v>297186.25</v>
       </c>
     </row>
     <row r="7">
@@ -1067,35 +1067,35 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>573331.38</v>
+        <v>501433.28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>630884.38</v>
+        <v>552256.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>660233.56</v>
+        <v>570019.62</v>
       </c>
     </row>
     <row r="5">
@@ -1133,101 +1133,101 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>380662.78</v>
+        <v>573331.38</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>415286.34</v>
+        <v>630884.38</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>426695.91</v>
+        <v>660233.56</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>297186.25</v>
+        <v>380662.78</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>326093.03</v>
+        <v>415286.34</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>338562.25</v>
+        <v>426695.91</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>501433.28</v>
+        <v>297186.25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>552256.25</v>
+        <v>326093.03</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>570019.62</v>
+        <v>338562.25</v>
       </c>
     </row>
     <row r="17">

--- a/output/laminas_provinciales/prov_i_ingr_mean_a_2022_metropolitana.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_mean_a_2022_metropolitana.xlsx
@@ -80,7 +80,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:36</t>
+    <t xml:space="preserve">2026-09-25 21:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -760,7 +760,7 @@
         <v>507028.59</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>67980.1</v>
+        <v>67980.09</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>13.41</v>

--- a/output/laminas_provinciales/prov_i_ingr_mean_a_2022_metropolitana.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_mean_a_2022_metropolitana.xlsx
@@ -61,7 +61,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 21:36</t>
+    <t xml:space="preserve">2026-10-05 07:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
